--- a/docs/roadmap_backlog.xlsx
+++ b/docs/roadmap_backlog.xlsx
@@ -1,44 +1,25 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>2</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="2" baseType="lpstr">
-      <vt:lpstr>Backlog</vt:lpstr>
-      <vt:lpstr>Phase Summary</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <Company/>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AA80DB-2864-49DA-9085-2611393A5673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Backlog" sheetId="1" r:id="rId1"/>
+    <sheet name="Phase Summary" sheetId="2" r:id="rId2"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase">Backlog!$A$1:$J$21,Backlog!$A$24:$J$99</definedName>
+  </definedNames>
+  <calcPr calcId="171027"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>openpyxl</dc:creator>
-  <cp:lastModifiedBy>Unknown</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-19T13:44:40Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-19T13:44:40Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="307">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="314">
   <si>
     <t>Phase</t>
   </si>
@@ -208,9 +189,6 @@
     <t>List A – #1 / Phase 1</t>
   </si>
   <si>
-    <t>Schema + 53-item seed delivered. Finish import + full icon population this phase.</t>
-  </si>
-  <si>
     <t>PDF export / clean map export</t>
   </si>
   <si>
@@ -349,51 +327,30 @@
     <t>Weeks 1-10, parallel to A/B</t>
   </si>
   <si>
-    <t>Split-panel layout; data's already fetched — a fast win.</t>
-  </si>
-  <si>
     <t>Shareable link (encode lat/lng + active layer in the URL)</t>
   </si>
   <si>
-    <t>One-line param change — near-zero cost, ship immediately.</t>
-  </si>
-  <si>
     <t>PDF site report (wind + solar + soil analysis export)</t>
   </si>
   <si>
-    <t>Distinct from the design-canvas PDF export in Phase A — this is the energy/soil analysis report. The pdf skill handles generation. Also the thing monetization_framework needs to decide how to gate.</t>
-  </si>
-  <si>
     <t>Combined renewable score (single energy-potential badge: wind + solar)</t>
   </si>
   <si>
     <t>ROI/payback calculator (electricity bill + budget -&gt; payback years)</t>
   </si>
   <si>
-    <t>Uses existing wind/solar data — pairs naturally with bankability in the W track.</t>
-  </si>
-  <si>
     <t>Optimal install month recommender (seasonal solar + wind data)</t>
   </si>
   <si>
-    <t>Built on SmartSolarAdvisor's existing seasonal data.</t>
-  </si>
-  <si>
     <t>Onboarding tooltip tour (4-step walkthrough)</t>
   </si>
   <si>
     <t>Onboarding</t>
   </si>
   <si>
-    <t>Distinct from the broader 'onboarding' beginner-mode item in Phase D — this is a lightweight tour for the existing analysis-card UI, shippable now.</t>
-  </si>
-  <si>
     <t>Precipitation card — Option A (static: intensity badge, rainfall chart, guidance, soil-saturation estimate)</t>
   </si>
   <si>
-    <t>Ship this static version first (matches the SolarCard/WindDashboard pattern), per your own recommendation.</t>
-  </si>
-  <si>
     <t>Composite soil health score (0-100, weighted, with trend indicator)</t>
   </si>
   <si>
@@ -592,9 +549,6 @@
     <t>Energy Calculators</t>
   </si>
   <si>
-    <t>Contained scope, good quick win once content team has capacity.</t>
-  </si>
-  <si>
     <t>Field Calculators</t>
   </si>
   <si>
@@ -959,19 +913,67 @@
   </si>
   <si>
     <t>~Sep 2026 – Apr 2027</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>STATUS UPDATE 2026-08-30: schema, 171-species seed, companion-planting data, subcategory cleanup, and the derived layer field are all Done and applied to both the Neon dev branch and production. What remains - full icon population and the actual canvas merge (wiring /api/elements into the designer palette instead of static presets.json) - has NOT started and is blocked, waiting on Omar to source/create a real image per icon_key (the plant DB has zero images today). See future-concerns.md item 11.</t>
+  </si>
+  <si>
+    <t>Split-panel layout; data's already fetched - a fast win. Code-checked 2026-08-28: confirmed not built - no comparison UI/route exists yet in swales-services.</t>
+  </si>
+  <si>
+    <t>One-line param change - near-zero cost, ship immediately. STATUS UPDATE 2026-08-30: built and verified live - MapComponent.jsx's updateLocationAndTimeGeoInfo now mirrors the pin into ?lat=&amp;lng= via window.history.replaceState (the active layer was already encoded by the path itself), read back on mount via getUrlLocation() taking priority over stored location/geolocation. Added a Copy shareable link button (Share2 icon) next to the PDF-report button.</t>
+  </si>
+  <si>
+    <t>Distinct from the design-canvas PDF export in Phase A - this is the energy/soil analysis report. STATUS UPDATE 2026-08-28: built - utils/combinedReportPdf.js's generateCombinedReport already produces this (and more: water stress, flood risk, precipitation, elevation, sun position, contour), wired through the shared site-data cache (see status.md's 2026-08-27 entry). What's still open is the monetization gate, not the report itself - ReportAuthGateModal currently only checks login, not payment.</t>
+  </si>
+  <si>
+    <t>Code-checked 2026-08-28: confirmed not built - solar and wind scores/badges exist independently (SolarCard.jsx, WindDashboard.jsx) but no single combined wind+solar badge found.</t>
+  </si>
+  <si>
+    <t>Built on SmartSolarAdvisor's existing seasonal data. Code-checked 2026-08-28: the foundation is real (smartSolarAdvisor.js already computes bestMonth/worstMonth PV output) but it's framed around peak generation, not an install-timing recommendation, and doesn't factor wind data - still not started as its own feature.</t>
+  </si>
+  <si>
+    <t>Distinct from the broader 'onboarding' beginner-mode item in Phase D - this is a lightweight tour for the existing analysis-card UI, shippable now. Code-checked 2026-08-28: confirmed not built - no tour/walkthrough component found.</t>
+  </si>
+  <si>
+    <t>Ship this static version first (matches the SolarCard/WindDashboard pattern), per your own recommendation. STATUS UPDATE 2026-08-28: built - components/ui/PrecipitationCard.jsx exists, fully implemented (intensity badge, rain animation, guidance), wired into LayerDataPanel.jsx.</t>
+  </si>
+  <si>
+    <t>STATUS UPDATE 2026-08-28: built - components/ui/SoilCard.jsx's computeScore() already implements a 0-100 weighted soil health score with tiered guidance (Good/Fair/Poor).</t>
+  </si>
+  <si>
+    <t>Code-checked 2026-08-28: confirmed not built - no crop-suitability ranking logic found.</t>
+  </si>
+  <si>
+    <t>Code-checked 2026-08-28: confirmed not built - no saved-pins/localStorage-notes feature found.</t>
+  </si>
+  <si>
+    <t>Done 2026-09-13 - all 26 calculators live across 6 categories (Earthworks &amp; Permaculture, General Agriculture, Vertical Farming, Microgreens, Aquaculture &amp; Aquaponics, Energy). Folded in Energy Calculators (row 64) plus 3 net-new categories not originally scoped here. Each calculator: real hand-verified formula/methodology, SEO/GEO article + FAQ schema, standalone manual-entry (no map/API dependency). Hub page at /field-calculators. See status.md's 2026-09-13 entries for full build/sourcing detail. swales-services commits 111ddcb..290d5cf.</t>
+  </si>
+  <si>
+    <t>Done 2026-09-13 - folded into the Field Calculators row (65) rather than built separately; see that row's notes. All 8 energy calculators (solar array, hydro power, battery bank, inverter, wind output, solar/wind payback, biogas potential, hybrid system balancer) live under /field-calculators.</t>
+  </si>
+  <si>
+    <t>Uses existing wind/solar data - pairs naturally with bankability in the W track. Code-checked 2026-08-28: confirmed not built as a real calculator - SolarCard.jsx currently only has tooltip text manually explaining the payback math, no interactive calculator. Shipped 2026-09-13 as the Solar &amp; Wind ROI/Payback Calculator under Field Calculators (/field-calculators/solar-wind-payback-calculator) - real interactive calculator now exists, standalone rather than added to SolarCard.jsx.</t>
+  </si>
+  <si>
+    <t>Code-checked 2026-08-28: confirmed not built as a real calculator - SoilCard.jsx only has generic 'targeted amendment' guidance text, no kg/hectare dosing calculation. Shipped 2026-09-13 as the Soil Amendment Rate Calculator under Field Calculators (/field-calculators/amendment-rate-calculator) - real interactive calculator now exists, standalone rather than added to SoilCard.jsx.</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1013,7 +1015,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1333,39 +1335,24 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <sheets>
-    <sheet sheetId="1" name="Backlog" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Phase Summary" state="visible" r:id="rId5"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase">Backlog!$A$1:$J$21,Backlog!$A$24:$J$99</definedName>
-  </definedNames>
-  <calcPr calcId="171027"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J110"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="70.83203125" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" customWidth="1"/>
+    <col min="3" max="3" width="55.77734375" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="26.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" customWidth="1"/>
+    <col min="10" max="10" width="70.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1384,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1429,7 +1416,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1461,7 +1448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1493,7 +1480,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1525,7 +1512,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1557,7 +1544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1589,7 +1576,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1621,7 +1608,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1653,7 +1640,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1685,7 +1672,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1717,7 +1704,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1749,7 +1736,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -1774,18 +1761,14 @@
       <c r="H13" t="s">
         <v>51</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>STATUS UPDATE 2026-08-30: schema, 171-species seed, companion-planting data, subcategory cleanup, and the derived layer field are all Done and applied to both the Neon dev branch and production. What remains - full icon population and the actual canvas merge (wiring /api/elements into the designer palette instead of static presets.json) - has NOT started and is blocked, waiting on Omar to source/create a real image per icon_key (the plant DB has zero images today). See future-concerns.md item 11.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>298</v>
+      </c>
+      <c r="J13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -1793,10 +1776,10 @@
         <v>47</v>
       </c>
       <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
         <v>57</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>50</v>
@@ -1814,10 +1797,10 @@
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -1825,13 +1808,13 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
         <v>60</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>62</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -1846,10 +1829,10 @@
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1857,13 +1840,13 @@
         <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
         <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>62</v>
       </c>
       <c r="F16" t="s">
         <v>34</v>
@@ -1878,10 +1861,10 @@
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1889,13 +1872,13 @@
         <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" t="s">
         <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>62</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -1910,10 +1893,10 @@
         <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1921,16 +1904,16 @@
         <v>47</v>
       </c>
       <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
         <v>68</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>69</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>70</v>
-      </c>
-      <c r="F18" t="s">
-        <v>71</v>
       </c>
       <c r="G18" t="s">
         <v>16</v>
@@ -1942,10 +1925,10 @@
         <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1953,13 +1936,13 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
         <v>73</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>75</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -1974,10 +1957,10 @@
         <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -1985,13 +1968,13 @@
         <v>47</v>
       </c>
       <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
         <v>77</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>78</v>
-      </c>
-      <c r="E20" t="s">
-        <v>79</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
@@ -2006,10 +1989,10 @@
         <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -2017,16 +2000,16 @@
         <v>47</v>
       </c>
       <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
         <v>81</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" t="s">
         <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" t="s">
-        <v>83</v>
       </c>
       <c r="G21" t="s">
         <v>16</v>
@@ -2038,10 +2021,10 @@
         <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -2049,16 +2032,16 @@
         <v>47</v>
       </c>
       <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="s">
         <v>85</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>86</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>87</v>
-      </c>
-      <c r="F22" t="s">
-        <v>88</v>
       </c>
       <c r="G22" t="s">
         <v>21</v>
@@ -2070,10 +2053,10 @@
         <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -2081,13 +2064,13 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" t="s">
         <v>86</v>
-      </c>
-      <c r="E23" t="s">
-        <v>87</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -2102,10 +2085,10 @@
         <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -2113,13 +2096,13 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -2134,10 +2117,10 @@
         <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -2145,13 +2128,13 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>54</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -2166,24 +2149,24 @@
         <v>25</v>
       </c>
       <c r="J25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>97</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>98</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>99</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>100</v>
-      </c>
-      <c r="E26" t="s">
-        <v>101</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -2192,32 +2175,30 @@
         <v>16</v>
       </c>
       <c r="H26" t="s">
+        <v>101</v>
+      </c>
+      <c r="I26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
         <v>102</v>
       </c>
-      <c r="I26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Split-panel layout; data's already fetched - a fast win. Code-checked 2026-08-28: confirmed not built - no comparison UI/route exists yet in swales-services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
       <c r="D27" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
         <v>100</v>
-      </c>
-      <c r="E27" t="s">
-        <v>101</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -2226,34 +2207,30 @@
         <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>102</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>One-line param change - near-zero cost, ship immediately. STATUS UPDATE 2026-08-30: built and verified live - MapComponent.jsx's updateLocationAndTimeGeoInfo now mirrors the pin into ?lat=&amp;lng= via window.history.replaceState (the active layer was already encoded by the path itself), read back on mount via getUrlLocation() taking priority over stored location/geolocation. Added a Copy shareable link button (Share2 icon) next to the PDF-report button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
         <v>97</v>
       </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s">
         <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>101</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -2262,34 +2239,30 @@
         <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>102</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Distinct from the design-canvas PDF export in Phase A - this is the energy/soil analysis report. STATUS UPDATE 2026-08-28: built - utils/combinedReportPdf.js's generateCombinedReport already produces this (and more: water stress, flood risk, precipitation, elevation, sun position, contour), wired through the shared site-data cache (see status.md's 2026-08-27 entry). What's still open is the monetization gate, not the report itself - ReportAuthGateModal currently only checks login, not payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" t="s">
         <v>97</v>
       </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" t="s">
         <v>100</v>
-      </c>
-      <c r="E29" t="s">
-        <v>101</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -2298,32 +2271,30 @@
         <v>21</v>
       </c>
       <c r="H29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Code-checked 2026-08-28: confirmed not built - solar and wind scores/badges exist independently (SolarCard.jsx, WindDashboard.jsx) but no single combined wind+solar badge found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
         <v>97</v>
       </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" t="s">
         <v>100</v>
-      </c>
-      <c r="E30" t="s">
-        <v>101</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -2332,32 +2303,30 @@
         <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Uses existing wind/solar data - pairs naturally with bankability in the W track. Code-checked 2026-08-28: confirmed not built as a real calculator - SolarCard.jsx currently only has tooltip text manually explaining the payback math, no interactive calculator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" t="s">
         <v>97</v>
       </c>
-      <c r="B31" t="s">
-        <v>98</v>
-      </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" t="s">
         <v>100</v>
-      </c>
-      <c r="E31" t="s">
-        <v>101</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -2366,32 +2335,30 @@
         <v>21</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Built on SmartSolarAdvisor's existing seasonal data. Code-checked 2026-08-28: the foundation is real (smartSolarAdvisor.js already computes bestMonth/worstMonth PV output) but it's framed around peak generation, not an install-timing recommendation, and doesn't factor wind data - still not started as its own feature.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J31" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
         <v>97</v>
       </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -2400,32 +2367,30 @@
         <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Distinct from the broader 'onboarding' beginner-mode item in Phase D - this is a lightweight tour for the existing analysis-card UI, shippable now. Code-checked 2026-08-28: confirmed not built - no tour/walkthrough component found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J32" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" t="s">
         <v>97</v>
       </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" t="s">
         <v>100</v>
-      </c>
-      <c r="E33" t="s">
-        <v>101</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -2434,34 +2399,30 @@
         <v>21</v>
       </c>
       <c r="H33" t="s">
-        <v>102</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Ship this static version first (matches the SolarCard/WindDashboard pattern), per your own recommendation. STATUS UPDATE 2026-08-28: built - components/ui/PrecipitationCard.jsx exists, fully implemented (intensity badge, rain animation, guidance), wired into LayerDataPanel.jsx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="I33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
         <v>97</v>
       </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" t="s">
         <v>100</v>
-      </c>
-      <c r="E34" t="s">
-        <v>101</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -2470,34 +2431,30 @@
         <v>21</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>STATUS UPDATE 2026-08-28: built - components/ui/SoilCard.jsx's computeScore() already implements a 0-100 weighted soil health score with tiered guidance (Good/Fair/Poor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="I34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
         <v>97</v>
       </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" t="s">
         <v>100</v>
-      </c>
-      <c r="E35" t="s">
-        <v>101</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -2506,32 +2463,30 @@
         <v>21</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Code-checked 2026-08-28: confirmed not built - no crop-suitability ranking logic found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J35" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s">
         <v>97</v>
       </c>
-      <c r="B36" t="s">
-        <v>98</v>
-      </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -2540,32 +2495,30 @@
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Code-checked 2026-08-28: confirmed not built as a real calculator - SoilCard.jsx only has generic 'targeted amendment' guidance text, no kg/hectare dosing calculation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s">
         <v>97</v>
       </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -2574,30 +2527,30 @@
         <v>21</v>
       </c>
       <c r="H37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
       </c>
       <c r="J37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
         <v>97</v>
       </c>
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -2606,898 +2559,899 @@
         <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" t="s">
         <v>97</v>
       </c>
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" t="s">
         <v>100</v>
-      </c>
-      <c r="E39" t="s">
-        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I39" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
         <v>97</v>
       </c>
-      <c r="B40" t="s">
-        <v>98</v>
-      </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" t="s">
         <v>100</v>
-      </c>
-      <c r="E40" t="s">
-        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
       </c>
       <c r="G40" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I40" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" t="s">
-        <v>98</v>
-      </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" t="s">
         <v>100</v>
-      </c>
-      <c r="E41" t="s">
-        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I41" t="s">
         <v>25</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Code-checked 2026-08-28: confirmed not built - no saved-pins/localStorage-notes feature found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J41" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" t="s">
         <v>97</v>
       </c>
-      <c r="B42" t="s">
-        <v>98</v>
-      </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
       </c>
       <c r="G42" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
       </c>
       <c r="J42" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" t="s">
         <v>97</v>
       </c>
-      <c r="B43" t="s">
-        <v>98</v>
-      </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" t="s">
         <v>100</v>
-      </c>
-      <c r="E43" t="s">
-        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
       </c>
       <c r="G43" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I43" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
         <v>97</v>
       </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" t="s">
         <v>100</v>
-      </c>
-      <c r="E44" t="s">
-        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I44" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
         <v>97</v>
       </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" t="s">
         <v>100</v>
-      </c>
-      <c r="E45" t="s">
-        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
       </c>
       <c r="G45" t="s">
+        <v>119</v>
+      </c>
+      <c r="H45" t="s">
+        <v>101</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>127</v>
       </c>
-      <c r="H45" t="s">
-        <v>102</v>
-      </c>
-      <c r="I45" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>135</v>
-      </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E46" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s">
         <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I46" t="s">
         <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D47" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s">
         <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I47" t="s">
         <v>25</v>
       </c>
       <c r="J47" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" t="s">
         <v>135</v>
       </c>
-      <c r="B48" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48" t="s">
-        <v>143</v>
-      </c>
       <c r="D48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s">
         <v>16</v>
       </c>
       <c r="H48" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I48" t="s">
         <v>25</v>
       </c>
       <c r="J48" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D49" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" t="s">
         <v>78</v>
       </c>
-      <c r="E49" t="s">
-        <v>79</v>
-      </c>
       <c r="F49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s">
         <v>16</v>
       </c>
       <c r="H49" t="s">
+        <v>131</v>
+      </c>
+      <c r="I49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" t="s">
         <v>139</v>
       </c>
-      <c r="I49" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>135</v>
-      </c>
-      <c r="B50" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" t="s">
-        <v>147</v>
-      </c>
       <c r="D50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E50" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G50" t="s">
         <v>21</v>
       </c>
       <c r="H50" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I50" t="s">
         <v>25</v>
       </c>
       <c r="J50" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C51" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s">
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I51" t="s">
         <v>25</v>
       </c>
       <c r="J51" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s">
         <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I52" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>141</v>
+      </c>
+      <c r="B53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53" t="s">
+        <v>148</v>
+      </c>
+      <c r="D53" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" t="s">
         <v>149</v>
       </c>
-      <c r="B53" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" t="s">
-        <v>156</v>
-      </c>
-      <c r="D53" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" t="s">
-        <v>157</v>
-      </c>
       <c r="F53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s">
         <v>21</v>
       </c>
       <c r="H53" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I53" t="s">
         <v>25</v>
       </c>
       <c r="J53" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E54" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s">
         <v>21</v>
       </c>
       <c r="H54" t="s">
+        <v>145</v>
+      </c>
+      <c r="I54" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" t="s">
         <v>153</v>
       </c>
-      <c r="I54" t="s">
-        <v>25</v>
-      </c>
-      <c r="J54" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>149</v>
-      </c>
-      <c r="B55" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" t="s">
-        <v>161</v>
-      </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E55" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F55" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G55" t="s">
         <v>21</v>
       </c>
       <c r="H55" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I55" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C56" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s">
         <v>21</v>
       </c>
       <c r="H56" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I56" t="s">
         <v>25</v>
       </c>
       <c r="J56" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" t="s">
+        <v>142</v>
+      </c>
+      <c r="C57" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" t="s">
+        <v>144</v>
+      </c>
+      <c r="E57" t="s">
+        <v>149</v>
+      </c>
+      <c r="F57" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s">
+        <v>119</v>
+      </c>
+      <c r="H57" t="s">
+        <v>145</v>
+      </c>
+      <c r="I57" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" t="s">
+        <v>130</v>
+      </c>
+      <c r="F58" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s">
+        <v>119</v>
+      </c>
+      <c r="H58" t="s">
+        <v>145</v>
+      </c>
+      <c r="I58" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
+        <v>161</v>
+      </c>
+      <c r="D59" t="s">
+        <v>144</v>
+      </c>
+      <c r="E59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F59" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s">
+        <v>119</v>
+      </c>
+      <c r="H59" t="s">
+        <v>145</v>
+      </c>
+      <c r="I59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>163</v>
+      </c>
+      <c r="B60" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>149</v>
-      </c>
-      <c r="B57" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="C60" t="s">
         <v>165</v>
       </c>
-      <c r="D57" t="s">
-        <v>152</v>
-      </c>
-      <c r="E57" t="s">
-        <v>157</v>
-      </c>
-      <c r="F57" t="s">
-        <v>83</v>
-      </c>
-      <c r="G57" t="s">
-        <v>127</v>
-      </c>
-      <c r="H57" t="s">
-        <v>153</v>
-      </c>
-      <c r="I57" t="s">
-        <v>25</v>
-      </c>
-      <c r="J57" t="s">
+      <c r="D60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>149</v>
-      </c>
-      <c r="B58" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" t="s">
-        <v>167</v>
-      </c>
-      <c r="D58" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" t="s">
-        <v>138</v>
-      </c>
-      <c r="F58" t="s">
-        <v>83</v>
-      </c>
-      <c r="G58" t="s">
-        <v>127</v>
-      </c>
-      <c r="H58" t="s">
-        <v>153</v>
-      </c>
-      <c r="I58" t="s">
-        <v>25</v>
-      </c>
-      <c r="J58" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>149</v>
-      </c>
-      <c r="B59" t="s">
-        <v>150</v>
-      </c>
-      <c r="C59" t="s">
-        <v>169</v>
-      </c>
-      <c r="D59" t="s">
-        <v>152</v>
-      </c>
-      <c r="E59" t="s">
-        <v>138</v>
-      </c>
-      <c r="F59" t="s">
-        <v>83</v>
-      </c>
-      <c r="G59" t="s">
-        <v>127</v>
-      </c>
-      <c r="H59" t="s">
-        <v>153</v>
-      </c>
-      <c r="I59" t="s">
-        <v>25</v>
-      </c>
-      <c r="J59" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>171</v>
-      </c>
-      <c r="B60" t="s">
-        <v>172</v>
-      </c>
-      <c r="C60" t="s">
-        <v>173</v>
-      </c>
-      <c r="D60" t="s">
-        <v>114</v>
-      </c>
-      <c r="E60" t="s">
-        <v>174</v>
-      </c>
       <c r="F60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G60" t="s">
         <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I60" t="s">
         <v>25</v>
       </c>
       <c r="J60" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C61" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D61" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E61" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G61" t="s">
         <v>21</v>
       </c>
       <c r="H61" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I61" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>163</v>
+      </c>
+      <c r="B62" t="s">
+        <v>164</v>
+      </c>
+      <c r="C62" t="s">
         <v>171</v>
-      </c>
-      <c r="B62" t="s">
-        <v>172</v>
-      </c>
-      <c r="C62" t="s">
-        <v>179</v>
       </c>
       <c r="D62" t="s">
         <v>54</v>
       </c>
       <c r="E62" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G62" t="s">
         <v>21</v>
       </c>
       <c r="H62" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I62" t="s">
         <v>25</v>
       </c>
       <c r="J62" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D63" t="s">
         <v>54</v>
       </c>
       <c r="E63" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G63" t="s">
         <v>21</v>
       </c>
       <c r="H63" t="s">
+        <v>167</v>
+      </c>
+      <c r="I63" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" t="s">
         <v>175</v>
       </c>
-      <c r="I63" t="s">
-        <v>25</v>
-      </c>
-      <c r="J63" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>171</v>
-      </c>
-      <c r="B64" t="s">
-        <v>172</v>
-      </c>
-      <c r="C64" t="s">
-        <v>183</v>
-      </c>
       <c r="D64" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G64" t="s">
         <v>21</v>
       </c>
       <c r="H64" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J64" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B65" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C65" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D65" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G65" t="s">
         <v>21</v>
       </c>
       <c r="H65" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I65" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="J65" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D66" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E66" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G66" t="s">
         <v>21</v>
       </c>
       <c r="H66" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I66" t="s">
         <v>25</v>
       </c>
       <c r="J66" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B67" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D67" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E67" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -3506,960 +3460,960 @@
         <v>21</v>
       </c>
       <c r="H67" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I67" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C68" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D68" t="s">
         <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H68" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I68" t="s">
         <v>25</v>
       </c>
       <c r="J68" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B69" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C69" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D69" t="s">
         <v>54</v>
       </c>
       <c r="E69" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H69" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I69" t="s">
         <v>25</v>
       </c>
       <c r="J69" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B70" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C70" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D70" t="s">
         <v>54</v>
       </c>
       <c r="E70" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G70" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H70" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I70" t="s">
         <v>25</v>
       </c>
       <c r="J70" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B71" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C71" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D71" t="s">
         <v>54</v>
       </c>
       <c r="E71" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G71" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H71" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I71" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C72" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" t="s">
+        <v>170</v>
+      </c>
+      <c r="E72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F72" t="s">
+        <v>70</v>
+      </c>
+      <c r="G72" t="s">
+        <v>119</v>
+      </c>
+      <c r="H72" t="s">
+        <v>167</v>
+      </c>
+      <c r="I72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C73" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" t="s">
+        <v>130</v>
+      </c>
+      <c r="F73" t="s">
+        <v>70</v>
+      </c>
+      <c r="G73" t="s">
+        <v>119</v>
+      </c>
+      <c r="H73" t="s">
+        <v>167</v>
+      </c>
+      <c r="I73" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" t="s">
+        <v>164</v>
+      </c>
+      <c r="C74" t="s">
+        <v>192</v>
+      </c>
+      <c r="D74" t="s">
+        <v>170</v>
+      </c>
+      <c r="E74" t="s">
+        <v>130</v>
+      </c>
+      <c r="F74" t="s">
+        <v>70</v>
+      </c>
+      <c r="G74" t="s">
+        <v>119</v>
+      </c>
+      <c r="H74" t="s">
+        <v>167</v>
+      </c>
+      <c r="I74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" t="s">
+        <v>194</v>
+      </c>
+      <c r="D75" t="s">
+        <v>170</v>
+      </c>
+      <c r="E75" t="s">
+        <v>130</v>
+      </c>
+      <c r="F75" t="s">
+        <v>70</v>
+      </c>
+      <c r="G75" t="s">
+        <v>119</v>
+      </c>
+      <c r="H75" t="s">
+        <v>167</v>
+      </c>
+      <c r="I75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>195</v>
+      </c>
+      <c r="B76" t="s">
+        <v>196</v>
+      </c>
+      <c r="C76" t="s">
+        <v>197</v>
+      </c>
+      <c r="D76" t="s">
         <v>198</v>
       </c>
-      <c r="D72" t="s">
-        <v>178</v>
-      </c>
-      <c r="E72" t="s">
-        <v>138</v>
-      </c>
-      <c r="F72" t="s">
-        <v>71</v>
-      </c>
-      <c r="G72" t="s">
-        <v>127</v>
-      </c>
-      <c r="H72" t="s">
-        <v>175</v>
-      </c>
-      <c r="I72" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>171</v>
-      </c>
-      <c r="B73" t="s">
-        <v>172</v>
-      </c>
-      <c r="C73" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" t="s">
-        <v>178</v>
-      </c>
-      <c r="E73" t="s">
-        <v>138</v>
-      </c>
-      <c r="F73" t="s">
-        <v>71</v>
-      </c>
-      <c r="G73" t="s">
-        <v>127</v>
-      </c>
-      <c r="H73" t="s">
-        <v>175</v>
-      </c>
-      <c r="I73" t="s">
-        <v>25</v>
-      </c>
-      <c r="J73" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>171</v>
-      </c>
-      <c r="B74" t="s">
-        <v>172</v>
-      </c>
-      <c r="C74" t="s">
-        <v>201</v>
-      </c>
-      <c r="D74" t="s">
-        <v>178</v>
-      </c>
-      <c r="E74" t="s">
-        <v>138</v>
-      </c>
-      <c r="F74" t="s">
-        <v>71</v>
-      </c>
-      <c r="G74" t="s">
-        <v>127</v>
-      </c>
-      <c r="H74" t="s">
-        <v>175</v>
-      </c>
-      <c r="I74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J74" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>171</v>
-      </c>
-      <c r="B75" t="s">
-        <v>172</v>
-      </c>
-      <c r="C75" t="s">
-        <v>203</v>
-      </c>
-      <c r="D75" t="s">
-        <v>178</v>
-      </c>
-      <c r="E75" t="s">
-        <v>138</v>
-      </c>
-      <c r="F75" t="s">
-        <v>71</v>
-      </c>
-      <c r="G75" t="s">
-        <v>127</v>
-      </c>
-      <c r="H75" t="s">
-        <v>175</v>
-      </c>
-      <c r="I75" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>204</v>
-      </c>
-      <c r="B76" t="s">
-        <v>205</v>
-      </c>
-      <c r="C76" t="s">
-        <v>206</v>
-      </c>
-      <c r="D76" t="s">
-        <v>207</v>
-      </c>
       <c r="E76" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G76" t="s">
         <v>21</v>
       </c>
       <c r="H76" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I76" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B77" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D77" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E77" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G77" t="s">
         <v>21</v>
       </c>
       <c r="H77" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I77" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B78" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C78" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D78" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E78" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="F78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G78" t="s">
         <v>21</v>
       </c>
       <c r="H78" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I78" t="s">
         <v>25</v>
       </c>
       <c r="J78" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B79" t="s">
+        <v>196</v>
+      </c>
+      <c r="C79" t="s">
         <v>204</v>
       </c>
-      <c r="B79" t="s">
-        <v>205</v>
-      </c>
-      <c r="C79" t="s">
-        <v>213</v>
-      </c>
       <c r="D79" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E79" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G79" t="s">
         <v>21</v>
       </c>
       <c r="H79" t="s">
+        <v>199</v>
+      </c>
+      <c r="I79" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>195</v>
+      </c>
+      <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
+        <v>206</v>
+      </c>
+      <c r="D80" t="s">
+        <v>144</v>
+      </c>
+      <c r="E80" t="s">
+        <v>130</v>
+      </c>
+      <c r="F80" t="s">
+        <v>70</v>
+      </c>
+      <c r="G80" t="s">
+        <v>119</v>
+      </c>
+      <c r="H80" t="s">
+        <v>199</v>
+      </c>
+      <c r="I80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>195</v>
+      </c>
+      <c r="B81" t="s">
+        <v>196</v>
+      </c>
+      <c r="C81" t="s">
+        <v>207</v>
+      </c>
+      <c r="D81" t="s">
         <v>208</v>
       </c>
-      <c r="I79" t="s">
-        <v>25</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="E81" t="s">
+        <v>130</v>
+      </c>
+      <c r="F81" t="s">
+        <v>70</v>
+      </c>
+      <c r="G81" t="s">
+        <v>119</v>
+      </c>
+      <c r="H81" t="s">
+        <v>199</v>
+      </c>
+      <c r="I81" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>195</v>
+      </c>
+      <c r="B82" t="s">
+        <v>196</v>
+      </c>
+      <c r="C82" t="s">
+        <v>210</v>
+      </c>
+      <c r="D82" t="s">
+        <v>208</v>
+      </c>
+      <c r="E82" t="s">
+        <v>130</v>
+      </c>
+      <c r="F82" t="s">
+        <v>70</v>
+      </c>
+      <c r="G82" t="s">
+        <v>119</v>
+      </c>
+      <c r="H82" t="s">
+        <v>199</v>
+      </c>
+      <c r="I82" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>195</v>
+      </c>
+      <c r="B83" t="s">
+        <v>196</v>
+      </c>
+      <c r="C83" t="s">
+        <v>212</v>
+      </c>
+      <c r="D83" t="s">
+        <v>208</v>
+      </c>
+      <c r="E83" t="s">
+        <v>130</v>
+      </c>
+      <c r="F83" t="s">
+        <v>70</v>
+      </c>
+      <c r="G83" t="s">
+        <v>119</v>
+      </c>
+      <c r="H83" t="s">
+        <v>199</v>
+      </c>
+      <c r="I83" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>204</v>
-      </c>
-      <c r="B80" t="s">
-        <v>205</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B84" t="s">
         <v>215</v>
       </c>
-      <c r="D80" t="s">
-        <v>152</v>
-      </c>
-      <c r="E80" t="s">
-        <v>138</v>
-      </c>
-      <c r="F80" t="s">
-        <v>71</v>
-      </c>
-      <c r="G80" t="s">
-        <v>127</v>
-      </c>
-      <c r="H80" t="s">
-        <v>208</v>
-      </c>
-      <c r="I80" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>204</v>
-      </c>
-      <c r="B81" t="s">
-        <v>205</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="C84" t="s">
         <v>216</v>
-      </c>
-      <c r="D81" t="s">
-        <v>217</v>
-      </c>
-      <c r="E81" t="s">
-        <v>138</v>
-      </c>
-      <c r="F81" t="s">
-        <v>71</v>
-      </c>
-      <c r="G81" t="s">
-        <v>127</v>
-      </c>
-      <c r="H81" t="s">
-        <v>208</v>
-      </c>
-      <c r="I81" t="s">
-        <v>25</v>
-      </c>
-      <c r="J81" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B82" t="s">
-        <v>205</v>
-      </c>
-      <c r="C82" t="s">
-        <v>219</v>
-      </c>
-      <c r="D82" t="s">
-        <v>217</v>
-      </c>
-      <c r="E82" t="s">
-        <v>138</v>
-      </c>
-      <c r="F82" t="s">
-        <v>71</v>
-      </c>
-      <c r="G82" t="s">
-        <v>127</v>
-      </c>
-      <c r="H82" t="s">
-        <v>208</v>
-      </c>
-      <c r="I82" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>204</v>
-      </c>
-      <c r="B83" t="s">
-        <v>205</v>
-      </c>
-      <c r="C83" t="s">
-        <v>221</v>
-      </c>
-      <c r="D83" t="s">
-        <v>217</v>
-      </c>
-      <c r="E83" t="s">
-        <v>138</v>
-      </c>
-      <c r="F83" t="s">
-        <v>71</v>
-      </c>
-      <c r="G83" t="s">
-        <v>127</v>
-      </c>
-      <c r="H83" t="s">
-        <v>208</v>
-      </c>
-      <c r="I83" t="s">
-        <v>25</v>
-      </c>
-      <c r="J83" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>223</v>
-      </c>
-      <c r="B84" t="s">
-        <v>224</v>
-      </c>
-      <c r="C84" t="s">
-        <v>225</v>
       </c>
       <c r="D84" t="s">
         <v>49</v>
       </c>
       <c r="E84" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
       </c>
       <c r="G84" t="s">
+        <v>218</v>
+      </c>
+      <c r="H84" t="s">
+        <v>219</v>
+      </c>
+      <c r="I84" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>214</v>
+      </c>
+      <c r="B85" t="s">
+        <v>215</v>
+      </c>
+      <c r="C85" t="s">
+        <v>221</v>
+      </c>
+      <c r="D85" t="s">
+        <v>222</v>
+      </c>
+      <c r="E85" t="s">
+        <v>149</v>
+      </c>
+      <c r="F85" t="s">
+        <v>70</v>
+      </c>
+      <c r="G85" t="s">
+        <v>218</v>
+      </c>
+      <c r="H85" t="s">
+        <v>219</v>
+      </c>
+      <c r="I85" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>214</v>
+      </c>
+      <c r="B86" t="s">
+        <v>215</v>
+      </c>
+      <c r="C86" t="s">
+        <v>224</v>
+      </c>
+      <c r="D86" t="s">
+        <v>222</v>
+      </c>
+      <c r="E86" t="s">
+        <v>130</v>
+      </c>
+      <c r="F86" t="s">
+        <v>70</v>
+      </c>
+      <c r="G86" t="s">
+        <v>218</v>
+      </c>
+      <c r="H86" t="s">
+        <v>219</v>
+      </c>
+      <c r="I86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>214</v>
+      </c>
+      <c r="B87" t="s">
+        <v>215</v>
+      </c>
+      <c r="C87" t="s">
+        <v>225</v>
+      </c>
+      <c r="D87" t="s">
+        <v>222</v>
+      </c>
+      <c r="E87" t="s">
+        <v>130</v>
+      </c>
+      <c r="F87" t="s">
+        <v>70</v>
+      </c>
+      <c r="G87" t="s">
+        <v>218</v>
+      </c>
+      <c r="H87" t="s">
+        <v>219</v>
+      </c>
+      <c r="I87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>214</v>
+      </c>
+      <c r="B88" t="s">
+        <v>215</v>
+      </c>
+      <c r="C88" t="s">
         <v>227</v>
       </c>
-      <c r="H84" t="s">
+      <c r="D88" t="s">
+        <v>222</v>
+      </c>
+      <c r="E88" t="s">
+        <v>149</v>
+      </c>
+      <c r="F88" t="s">
+        <v>70</v>
+      </c>
+      <c r="G88" t="s">
+        <v>218</v>
+      </c>
+      <c r="H88" t="s">
+        <v>219</v>
+      </c>
+      <c r="I88" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" t="s">
         <v>228</v>
       </c>
-      <c r="I84" t="s">
-        <v>25</v>
-      </c>
-      <c r="J84" t="s">
+    </row>
+    <row r="89" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>214</v>
+      </c>
+      <c r="B89" t="s">
+        <v>215</v>
+      </c>
+      <c r="C89" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>223</v>
-      </c>
-      <c r="B85" t="s">
-        <v>224</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="D89" t="s">
+        <v>170</v>
+      </c>
+      <c r="E89" t="s">
+        <v>130</v>
+      </c>
+      <c r="F89" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" t="s">
+        <v>218</v>
+      </c>
+      <c r="H89" t="s">
+        <v>219</v>
+      </c>
+      <c r="I89" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" t="s">
         <v>230</v>
       </c>
-      <c r="D85" t="s">
+    </row>
+    <row r="90" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>214</v>
+      </c>
+      <c r="B90" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" t="s">
         <v>231</v>
       </c>
-      <c r="E85" t="s">
-        <v>157</v>
-      </c>
-      <c r="F85" t="s">
-        <v>71</v>
-      </c>
-      <c r="G85" t="s">
-        <v>227</v>
-      </c>
-      <c r="H85" t="s">
-        <v>228</v>
-      </c>
-      <c r="I85" t="s">
-        <v>25</v>
-      </c>
-      <c r="J85" t="s">
+      <c r="D90" t="s">
+        <v>170</v>
+      </c>
+      <c r="E90" t="s">
+        <v>130</v>
+      </c>
+      <c r="F90" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90" t="s">
+        <v>218</v>
+      </c>
+      <c r="H90" t="s">
+        <v>219</v>
+      </c>
+      <c r="I90" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>223</v>
-      </c>
-      <c r="B86" t="s">
-        <v>224</v>
-      </c>
-      <c r="C86" t="s">
+    <row r="91" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>214</v>
+      </c>
+      <c r="B91" t="s">
+        <v>215</v>
+      </c>
+      <c r="C91" t="s">
         <v>233</v>
       </c>
-      <c r="D86" t="s">
-        <v>231</v>
-      </c>
-      <c r="E86" t="s">
-        <v>138</v>
-      </c>
-      <c r="F86" t="s">
-        <v>71</v>
-      </c>
-      <c r="G86" t="s">
-        <v>227</v>
-      </c>
-      <c r="H86" t="s">
-        <v>228</v>
-      </c>
-      <c r="I86" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>223</v>
-      </c>
-      <c r="B87" t="s">
-        <v>224</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="D91" t="s">
+        <v>170</v>
+      </c>
+      <c r="E91" t="s">
+        <v>130</v>
+      </c>
+      <c r="F91" t="s">
+        <v>70</v>
+      </c>
+      <c r="G91" t="s">
+        <v>218</v>
+      </c>
+      <c r="H91" t="s">
+        <v>219</v>
+      </c>
+      <c r="I91" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" t="s">
+        <v>215</v>
+      </c>
+      <c r="C92" t="s">
         <v>234</v>
       </c>
-      <c r="D87" t="s">
-        <v>231</v>
-      </c>
-      <c r="E87" t="s">
-        <v>138</v>
-      </c>
-      <c r="F87" t="s">
-        <v>71</v>
-      </c>
-      <c r="G87" t="s">
-        <v>227</v>
-      </c>
-      <c r="H87" t="s">
-        <v>228</v>
-      </c>
-      <c r="I87" t="s">
-        <v>25</v>
-      </c>
-      <c r="J87" t="s">
+      <c r="D92" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>223</v>
-      </c>
-      <c r="B88" t="s">
-        <v>224</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="E92" t="s">
+        <v>130</v>
+      </c>
+      <c r="F92" t="s">
+        <v>70</v>
+      </c>
+      <c r="G92" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" t="s">
+        <v>219</v>
+      </c>
+      <c r="I92" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" t="s">
         <v>236</v>
       </c>
-      <c r="D88" t="s">
-        <v>231</v>
-      </c>
-      <c r="E88" t="s">
-        <v>157</v>
-      </c>
-      <c r="F88" t="s">
-        <v>71</v>
-      </c>
-      <c r="G88" t="s">
-        <v>227</v>
-      </c>
-      <c r="H88" t="s">
-        <v>228</v>
-      </c>
-      <c r="I88" t="s">
-        <v>25</v>
-      </c>
-      <c r="J88" t="s">
+    </row>
+    <row r="93" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>214</v>
+      </c>
+      <c r="B93" t="s">
+        <v>215</v>
+      </c>
+      <c r="C93" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>223</v>
-      </c>
-      <c r="B89" t="s">
-        <v>224</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="D93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E93" t="s">
+        <v>130</v>
+      </c>
+      <c r="F93" t="s">
+        <v>70</v>
+      </c>
+      <c r="G93" t="s">
+        <v>218</v>
+      </c>
+      <c r="H93" t="s">
+        <v>219</v>
+      </c>
+      <c r="I93" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" t="s">
         <v>238</v>
       </c>
-      <c r="D89" t="s">
-        <v>178</v>
-      </c>
-      <c r="E89" t="s">
-        <v>138</v>
-      </c>
-      <c r="F89" t="s">
-        <v>71</v>
-      </c>
-      <c r="G89" t="s">
-        <v>227</v>
-      </c>
-      <c r="H89" t="s">
-        <v>228</v>
-      </c>
-      <c r="I89" t="s">
-        <v>25</v>
-      </c>
-      <c r="J89" t="s">
+    </row>
+    <row r="94" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>214</v>
+      </c>
+      <c r="B94" t="s">
+        <v>215</v>
+      </c>
+      <c r="C94" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>223</v>
-      </c>
-      <c r="B90" t="s">
-        <v>224</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="D94" t="s">
+        <v>235</v>
+      </c>
+      <c r="E94" t="s">
+        <v>130</v>
+      </c>
+      <c r="F94" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" t="s">
+        <v>218</v>
+      </c>
+      <c r="H94" t="s">
+        <v>219</v>
+      </c>
+      <c r="I94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" t="s">
+        <v>215</v>
+      </c>
+      <c r="C95" t="s">
         <v>240</v>
       </c>
-      <c r="D90" t="s">
-        <v>178</v>
-      </c>
-      <c r="E90" t="s">
-        <v>138</v>
-      </c>
-      <c r="F90" t="s">
-        <v>71</v>
-      </c>
-      <c r="G90" t="s">
-        <v>227</v>
-      </c>
-      <c r="H90" t="s">
-        <v>228</v>
-      </c>
-      <c r="I90" t="s">
-        <v>25</v>
-      </c>
-      <c r="J90" t="s">
+      <c r="D95" t="s">
+        <v>222</v>
+      </c>
+      <c r="E95" t="s">
+        <v>149</v>
+      </c>
+      <c r="F95" t="s">
+        <v>70</v>
+      </c>
+      <c r="G95" t="s">
+        <v>218</v>
+      </c>
+      <c r="H95" t="s">
+        <v>219</v>
+      </c>
+      <c r="I95" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>223</v>
-      </c>
-      <c r="B91" t="s">
-        <v>224</v>
-      </c>
-      <c r="C91" t="s">
+    <row r="96" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" t="s">
         <v>242</v>
       </c>
-      <c r="D91" t="s">
-        <v>178</v>
-      </c>
-      <c r="E91" t="s">
-        <v>138</v>
-      </c>
-      <c r="F91" t="s">
-        <v>71</v>
-      </c>
-      <c r="G91" t="s">
-        <v>227</v>
-      </c>
-      <c r="H91" t="s">
-        <v>228</v>
-      </c>
-      <c r="I91" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>223</v>
-      </c>
-      <c r="B92" t="s">
-        <v>224</v>
-      </c>
-      <c r="C92" t="s">
-        <v>243</v>
-      </c>
-      <c r="D92" t="s">
-        <v>244</v>
-      </c>
-      <c r="E92" t="s">
-        <v>138</v>
-      </c>
-      <c r="F92" t="s">
-        <v>71</v>
-      </c>
-      <c r="G92" t="s">
-        <v>227</v>
-      </c>
-      <c r="H92" t="s">
-        <v>228</v>
-      </c>
-      <c r="I92" t="s">
-        <v>25</v>
-      </c>
-      <c r="J92" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>223</v>
-      </c>
-      <c r="B93" t="s">
-        <v>224</v>
-      </c>
-      <c r="C93" t="s">
-        <v>246</v>
-      </c>
-      <c r="D93" t="s">
-        <v>244</v>
-      </c>
-      <c r="E93" t="s">
-        <v>138</v>
-      </c>
-      <c r="F93" t="s">
-        <v>71</v>
-      </c>
-      <c r="G93" t="s">
-        <v>227</v>
-      </c>
-      <c r="H93" t="s">
-        <v>228</v>
-      </c>
-      <c r="I93" t="s">
-        <v>25</v>
-      </c>
-      <c r="J93" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>223</v>
-      </c>
-      <c r="B94" t="s">
-        <v>224</v>
-      </c>
-      <c r="C94" t="s">
-        <v>248</v>
-      </c>
-      <c r="D94" t="s">
-        <v>244</v>
-      </c>
-      <c r="E94" t="s">
-        <v>138</v>
-      </c>
-      <c r="F94" t="s">
-        <v>71</v>
-      </c>
-      <c r="G94" t="s">
-        <v>227</v>
-      </c>
-      <c r="H94" t="s">
-        <v>228</v>
-      </c>
-      <c r="I94" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>223</v>
-      </c>
-      <c r="B95" t="s">
-        <v>224</v>
-      </c>
-      <c r="C95" t="s">
-        <v>249</v>
-      </c>
-      <c r="D95" t="s">
-        <v>231</v>
-      </c>
-      <c r="E95" t="s">
-        <v>157</v>
-      </c>
-      <c r="F95" t="s">
-        <v>71</v>
-      </c>
-      <c r="G95" t="s">
-        <v>227</v>
-      </c>
-      <c r="H95" t="s">
-        <v>228</v>
-      </c>
-      <c r="I95" t="s">
-        <v>25</v>
-      </c>
-      <c r="J95" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>223</v>
-      </c>
-      <c r="B96" t="s">
-        <v>224</v>
-      </c>
-      <c r="C96" t="s">
-        <v>251</v>
-      </c>
       <c r="D96" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E96" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F96" t="s">
         <v>34</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H96" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="I96" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B97" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C97" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D97" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E97" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F97" t="s">
         <v>34</v>
       </c>
       <c r="G97" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H97" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="I97" t="s">
         <v>25</v>
       </c>
       <c r="J97" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C98" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D98" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E98" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -4468,30 +4422,30 @@
         <v>16</v>
       </c>
       <c r="H98" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I98" t="s">
         <v>25</v>
       </c>
       <c r="J98" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B99" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C99" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D99" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E99" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -4500,30 +4454,30 @@
         <v>16</v>
       </c>
       <c r="H99" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I99" t="s">
         <v>25</v>
       </c>
       <c r="J99" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>245</v>
+      </c>
+      <c r="B100" t="s">
+        <v>246</v>
+      </c>
+      <c r="C100" t="s">
         <v>254</v>
       </c>
-      <c r="B100" t="s">
+      <c r="D100" t="s">
+        <v>57</v>
+      </c>
+      <c r="E100" t="s">
         <v>255</v>
-      </c>
-      <c r="C100" t="s">
-        <v>263</v>
-      </c>
-      <c r="D100" t="s">
-        <v>58</v>
-      </c>
-      <c r="E100" t="s">
-        <v>264</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -4532,30 +4486,30 @@
         <v>16</v>
       </c>
       <c r="H100" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I100" t="s">
         <v>25</v>
       </c>
       <c r="J100" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B101" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C101" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D101" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E101" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -4564,30 +4518,30 @@
         <v>21</v>
       </c>
       <c r="H101" t="s">
+        <v>249</v>
+      </c>
+      <c r="I101" t="s">
+        <v>25</v>
+      </c>
+      <c r="J101" t="s">
         <v>258</v>
       </c>
-      <c r="I101" t="s">
-        <v>25</v>
-      </c>
-      <c r="J101" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C102" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
         <v>49</v>
       </c>
       <c r="E102" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -4596,27 +4550,27 @@
         <v>21</v>
       </c>
       <c r="H102" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I102" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B103" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C103" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="D103" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E103" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -4625,27 +4579,27 @@
         <v>21</v>
       </c>
       <c r="H103" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I103" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C104" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D104" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E104" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -4654,27 +4608,27 @@
         <v>21</v>
       </c>
       <c r="H104" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I104" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B105" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C105" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E105" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -4683,205 +4637,206 @@
         <v>21</v>
       </c>
       <c r="H105" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I105" t="s">
         <v>25</v>
       </c>
       <c r="J105" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B106" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C106" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E106" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
       </c>
       <c r="G106" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H106" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I106" t="s">
         <v>25</v>
       </c>
       <c r="J106" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C107" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D107" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E107" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H107" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I107" t="s">
         <v>25</v>
       </c>
       <c r="J107" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C108" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="D108" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E108" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H108" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I108" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B109" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C109" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D109" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E109" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H109" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I109" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B110" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C110" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D110" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E110" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F110" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="G110" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="H110" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="I110" t="s">
         <v>25</v>
       </c>
       <c r="J110" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" customWidth="1"/>
-    <col min="7" max="10" width="7.83203125" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" customWidth="1"/>
+    <col min="7" max="10" width="7.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="G1" t="s">
         <v>16</v>
@@ -4890,13 +4845,13 @@
         <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -4907,10 +4862,10 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -4928,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -4939,10 +4894,10 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F3">
         <v>14</v>
@@ -4960,21 +4915,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
         <v>97</v>
       </c>
-      <c r="B4" t="s">
-        <v>98</v>
-      </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -4992,21 +4947,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E5" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5024,21 +4979,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E6" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -5056,21 +5011,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E7" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="F7">
         <v>16</v>
@@ -5088,21 +5043,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E8" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -5120,21 +5075,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D9" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E9" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F9">
         <v>14</v>
@@ -5152,21 +5107,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B10" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C10" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="D10" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E10" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F10">
         <v>12</v>
@@ -5184,21 +5139,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -5217,5 +5172,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>